--- a/01_macro_economic/PCE/Z.economic_pulse_monthly/pce_real_detail.xlsx
+++ b/01_macro_economic/PCE/Z.economic_pulse_monthly/pce_real_detail.xlsx
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>113.924</v>
+        <v>113.643</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0.007971828742822318</v>
+        <v>0.00548560912380669</v>
       </c>
       <c r="L21" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -2524,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>163.382</v>
+        <v>161.941</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.07873521857688992</v>
+        <v>0.06922096700713731</v>
       </c>
       <c r="L41" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42">
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>136.042</v>
+        <v>135.459</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.01673355604881799</v>
+        <v>0.01237640411649976</v>
       </c>
       <c r="L61" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62">
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>130.118</v>
+        <v>129.244</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>0.04076082609460729</v>
+        <v>0.03377005647006115</v>
       </c>
       <c r="L81" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82">
@@ -5596,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>96.777</v>
+        <v>98.30200000000001</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>-0.04721727230661688</v>
+        <v>-0.03220343989052199</v>
       </c>
       <c r="L101" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
@@ -6620,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>110.485</v>
+        <v>110.745</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>0.05581782041970862</v>
+        <v>0.05830243492221254</v>
       </c>
       <c r="L121" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="122">
@@ -7644,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>131.939</v>
+        <v>133.488</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -7652,10 +7652,10 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>0.01219802223262167</v>
+        <v>0.02408150426930789</v>
       </c>
       <c r="L141" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="142">
@@ -8668,7 +8668,7 @@
         <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>115.209</v>
+        <v>115.391</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="K161" t="n">
-        <v>0.05132089245790938</v>
+        <v>0.05298170370032396</v>
       </c>
       <c r="L161" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="162">
@@ -9692,7 +9692,7 @@
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>149.672</v>
+        <v>149.693</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         </is>
       </c>
       <c r="K181" t="n">
-        <v>0.05720723584299248</v>
+        <v>0.05735556921164342</v>
       </c>
       <c r="L181" t="n">
         <v>71</v>
@@ -10716,7 +10716,7 @@
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>98.83499999999999</v>
+        <v>97.754</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="K201" t="n">
-        <v>-0.03014513232653304</v>
+        <v>-0.04075284327867557</v>
       </c>
       <c r="L201" t="n">
         <v>5</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="I221" t="n">
-        <v>108.53</v>
+        <v>107.397</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -11748,10 +11748,10 @@
         </is>
       </c>
       <c r="K221" t="n">
-        <v>0.01586558712032571</v>
+        <v>0.005260448354939884</v>
       </c>
       <c r="L221" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="222">
@@ -12764,7 +12764,7 @@
         <v>0</v>
       </c>
       <c r="I241" t="n">
-        <v>106.067</v>
+        <v>104.82</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -12772,10 +12772,10 @@
         </is>
       </c>
       <c r="K241" t="n">
-        <v>0.001529672819980066</v>
+        <v>-0.01024503092394136</v>
       </c>
       <c r="L241" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="242">
@@ -13799,7 +13799,7 @@
         <v>-0.001514554872323104</v>
       </c>
       <c r="L261" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="262">
@@ -14812,7 +14812,7 @@
         <v>0</v>
       </c>
       <c r="I281" t="n">
-        <v>136.024</v>
+        <v>135.899</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
@@ -14820,10 +14820,10 @@
         </is>
       </c>
       <c r="K281" t="n">
-        <v>-0.06192932608755619</v>
+        <v>-0.06279137127251655</v>
       </c>
       <c r="L281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -15836,7 +15836,7 @@
         <v>0</v>
       </c>
       <c r="I301" t="n">
-        <v>140.317</v>
+        <v>140.121</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -15844,10 +15844,10 @@
         </is>
       </c>
       <c r="K301" t="n">
-        <v>0.05917208895061821</v>
+        <v>0.05769259801627435</v>
       </c>
       <c r="L301" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="302">
@@ -16871,7 +16871,7 @@
         <v>0.009648750854541976</v>
       </c>
       <c r="L321" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="322">
@@ -17884,7 +17884,7 @@
         <v>0</v>
       </c>
       <c r="I341" t="n">
-        <v>109.549</v>
+        <v>109.613</v>
       </c>
       <c r="J341" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         </is>
       </c>
       <c r="K341" t="n">
-        <v>0.04469683965592885</v>
+        <v>0.04530716560813275</v>
       </c>
       <c r="L341" t="n">
         <v>63</v>
@@ -18908,7 +18908,7 @@
         <v>0</v>
       </c>
       <c r="I361" t="n">
-        <v>106.34</v>
+        <v>106.416</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -18916,10 +18916,10 @@
         </is>
       </c>
       <c r="K361" t="n">
-        <v>0.03370174875817744</v>
+        <v>0.03444052375258799</v>
       </c>
       <c r="L361" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="362">
@@ -19932,7 +19932,7 @@
         <v>0</v>
       </c>
       <c r="I381" t="n">
-        <v>118.413</v>
+        <v>118.8</v>
       </c>
       <c r="J381" t="inlineStr">
         <is>
@@ -19940,10 +19940,10 @@
         </is>
       </c>
       <c r="K381" t="n">
-        <v>0.002268399001227328</v>
+        <v>0.005544034872402515</v>
       </c>
       <c r="L381" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="382">
@@ -20956,7 +20956,7 @@
         <v>0</v>
       </c>
       <c r="I401" t="n">
-        <v>175.023</v>
+        <v>175.035</v>
       </c>
       <c r="J401" t="inlineStr">
         <is>
@@ -20964,10 +20964,10 @@
         </is>
       </c>
       <c r="K401" t="n">
-        <v>0.1058367873028709</v>
+        <v>0.1059126061463809</v>
       </c>
       <c r="L401" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="402">
@@ -21980,7 +21980,7 @@
         <v>0</v>
       </c>
       <c r="I421" t="n">
-        <v>85.982</v>
+        <v>86.568</v>
       </c>
       <c r="J421" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         </is>
       </c>
       <c r="K421" t="n">
-        <v>0.08345619274436422</v>
+        <v>0.09084035837145121</v>
       </c>
       <c r="L421" t="n">
         <v>85</v>
@@ -23004,7 +23004,7 @@
         <v>0</v>
       </c>
       <c r="I441" t="n">
-        <v>116.01</v>
+        <v>116.009</v>
       </c>
       <c r="J441" t="inlineStr">
         <is>
@@ -23012,10 +23012,10 @@
         </is>
       </c>
       <c r="K441" t="n">
-        <v>0.06234318052782917</v>
+        <v>0.06233402318638848</v>
       </c>
       <c r="L441" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="442">
@@ -24028,7 +24028,7 @@
         <v>0</v>
       </c>
       <c r="I461" t="n">
-        <v>128.637</v>
+        <v>127.74</v>
       </c>
       <c r="J461" t="inlineStr">
         <is>
@@ -24036,10 +24036,10 @@
         </is>
       </c>
       <c r="K461" t="n">
-        <v>0.02759160588897847</v>
+        <v>0.02042609619517011</v>
       </c>
       <c r="L461" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="462">
@@ -25052,7 +25052,7 @@
         <v>0</v>
       </c>
       <c r="I481" t="n">
-        <v>132.106</v>
+        <v>131.952</v>
       </c>
       <c r="J481" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         </is>
       </c>
       <c r="K481" t="n">
-        <v>0.03459996240837038</v>
+        <v>0.03339389762546197</v>
       </c>
       <c r="L481" t="n">
         <v>53</v>
@@ -26076,7 +26076,7 @@
         <v>0</v>
       </c>
       <c r="I501" t="n">
-        <v>97.068</v>
+        <v>95.407</v>
       </c>
       <c r="J501" t="inlineStr">
         <is>
@@ -26084,10 +26084,10 @@
         </is>
       </c>
       <c r="K501" t="n">
-        <v>-0.05286575727416432</v>
+        <v>-0.06907284897449417</v>
       </c>
       <c r="L501" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -27100,7 +27100,7 @@
         <v>0</v>
       </c>
       <c r="I521" t="n">
-        <v>171.1</v>
+        <v>171.246</v>
       </c>
       <c r="J521" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="K521" t="n">
-        <v>0.1745807275398332</v>
+        <v>0.1755829998146483</v>
       </c>
       <c r="L521" t="n">
         <v>92</v>
@@ -28135,7 +28135,7 @@
         <v>0.006354961451879415</v>
       </c>
       <c r="L541" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="542">
@@ -29148,7 +29148,7 @@
         <v>0</v>
       </c>
       <c r="I561" t="n">
-        <v>99.872</v>
+        <v>99.607</v>
       </c>
       <c r="J561" t="inlineStr">
         <is>
@@ -29156,10 +29156,10 @@
         </is>
       </c>
       <c r="K561" t="n">
-        <v>-0.001429785532170214</v>
+        <v>-0.004079388091786207</v>
       </c>
       <c r="L561" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="562">
@@ -30172,7 +30172,7 @@
         <v>0</v>
       </c>
       <c r="I581" t="n">
-        <v>104.075</v>
+        <v>103.618</v>
       </c>
       <c r="J581" t="inlineStr">
         <is>
@@ -30180,10 +30180,10 @@
         </is>
       </c>
       <c r="K581" t="n">
-        <v>-0.003141672174171273</v>
+        <v>-0.007518941026599002</v>
       </c>
       <c r="L581" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="582">
@@ -31196,7 +31196,7 @@
         <v>0</v>
       </c>
       <c r="I601" t="n">
-        <v>108.849</v>
+        <v>108.787</v>
       </c>
       <c r="J601" t="inlineStr">
         <is>
@@ -31204,10 +31204,10 @@
         </is>
       </c>
       <c r="K601" t="n">
-        <v>0.01059345638206999</v>
+        <v>0.01001782597392964</v>
       </c>
       <c r="L601" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="602">
@@ -32220,7 +32220,7 @@
         <v>0</v>
       </c>
       <c r="I621" t="n">
-        <v>128.146</v>
+        <v>128.257</v>
       </c>
       <c r="J621" t="inlineStr">
         <is>
@@ -32228,10 +32228,10 @@
         </is>
       </c>
       <c r="K621" t="n">
-        <v>0.04050926865707982</v>
+        <v>0.04141055725618537</v>
       </c>
       <c r="L621" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="622">
@@ -33244,7 +33244,7 @@
         <v>0</v>
       </c>
       <c r="I641" t="n">
-        <v>119.757</v>
+        <v>119.567</v>
       </c>
       <c r="J641" t="inlineStr">
         <is>
@@ -33252,10 +33252,10 @@
         </is>
       </c>
       <c r="K641" t="n">
-        <v>0.03944901572752846</v>
+        <v>0.03779988195674044</v>
       </c>
       <c r="L641" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="642">
@@ -34268,7 +34268,7 @@
         <v>0</v>
       </c>
       <c r="I661" t="n">
-        <v>113.874</v>
+        <v>113.867</v>
       </c>
       <c r="J661" t="inlineStr">
         <is>
@@ -34276,10 +34276,10 @@
         </is>
       </c>
       <c r="K661" t="n">
-        <v>0.01287057379455092</v>
+        <v>0.01280831117080417</v>
       </c>
       <c r="L661" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="662">
@@ -35292,7 +35292,7 @@
         <v>0</v>
       </c>
       <c r="I681" t="n">
-        <v>122.163</v>
+        <v>122.055</v>
       </c>
       <c r="J681" t="inlineStr">
         <is>
@@ -35300,10 +35300,10 @@
         </is>
       </c>
       <c r="K681" t="n">
-        <v>0.0359820217096336</v>
+        <v>0.03506614654002727</v>
       </c>
       <c r="L681" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="682">
@@ -36316,7 +36316,7 @@
         <v>0</v>
       </c>
       <c r="I701" t="n">
-        <v>109.282</v>
+        <v>109.394</v>
       </c>
       <c r="J701" t="inlineStr">
         <is>
@@ -36324,10 +36324,10 @@
         </is>
       </c>
       <c r="K701" t="n">
-        <v>0.06518899740725592</v>
+        <v>0.06628067918201852</v>
       </c>
       <c r="L701" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="702">
@@ -37340,7 +37340,7 @@
         <v>0</v>
       </c>
       <c r="I721" t="n">
-        <v>108.86</v>
+        <v>108.847</v>
       </c>
       <c r="J721" t="inlineStr">
         <is>
@@ -37348,10 +37348,10 @@
         </is>
       </c>
       <c r="K721" t="n">
-        <v>0.006443978070134859</v>
+        <v>0.00632378909608633</v>
       </c>
       <c r="L721" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="722">
@@ -38364,7 +38364,7 @@
         <v>0</v>
       </c>
       <c r="I741" t="n">
-        <v>130.689</v>
+        <v>132.191</v>
       </c>
       <c r="J741" t="inlineStr">
         <is>
@@ -38372,10 +38372,10 @@
         </is>
       </c>
       <c r="K741" t="n">
-        <v>0.04476812509493233</v>
+        <v>0.05677557579003745</v>
       </c>
       <c r="L741" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="742">
@@ -39388,7 +39388,7 @@
         <v>0</v>
       </c>
       <c r="I761" t="n">
-        <v>142.399</v>
+        <v>138.682</v>
       </c>
       <c r="J761" t="inlineStr">
         <is>
@@ -39396,10 +39396,10 @@
         </is>
       </c>
       <c r="K761" t="n">
-        <v>0.03000339961374587</v>
+        <v>0.003117518137300879</v>
       </c>
       <c r="L761" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
     </row>
     <row r="762">
@@ -40412,7 +40412,7 @@
         <v>0</v>
       </c>
       <c r="I781" t="n">
-        <v>107.949</v>
+        <v>108.031</v>
       </c>
       <c r="J781" t="inlineStr">
         <is>
@@ -40420,10 +40420,10 @@
         </is>
       </c>
       <c r="K781" t="n">
-        <v>-0.003498633778893812</v>
+        <v>-0.002741673436230663</v>
       </c>
       <c r="L781" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="782">
@@ -41436,7 +41436,7 @@
         <v>0</v>
       </c>
       <c r="I801" t="n">
-        <v>143.7</v>
+        <v>144.779</v>
       </c>
       <c r="J801" t="inlineStr">
         <is>
@@ -41444,10 +41444,10 @@
         </is>
       </c>
       <c r="K801" t="n">
-        <v>0.05991429224721001</v>
+        <v>0.06787286929198899</v>
       </c>
       <c r="L801" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="802">
@@ -42460,7 +42460,7 @@
         <v>0</v>
       </c>
       <c r="I821" t="n">
-        <v>118.829</v>
+        <v>118.169</v>
       </c>
       <c r="J821" t="inlineStr">
         <is>
@@ -42468,10 +42468,10 @@
         </is>
       </c>
       <c r="K821" t="n">
-        <v>0.0158061207043938</v>
+        <v>0.01016413062061883</v>
       </c>
       <c r="L821" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="822">
@@ -43484,7 +43484,7 @@
         <v>0</v>
       </c>
       <c r="I841" t="n">
-        <v>98.90600000000001</v>
+        <v>98.78100000000001</v>
       </c>
       <c r="J841" t="inlineStr">
         <is>
@@ -43492,10 +43492,10 @@
         </is>
       </c>
       <c r="K841" t="n">
-        <v>-0.004959808448777081</v>
+        <v>-0.006217366371895072</v>
       </c>
       <c r="L841" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="842">
@@ -44508,7 +44508,7 @@
         <v>0</v>
       </c>
       <c r="I861" t="n">
-        <v>137.039</v>
+        <v>135.3</v>
       </c>
       <c r="J861" t="inlineStr">
         <is>
@@ -44516,10 +44516,10 @@
         </is>
       </c>
       <c r="K861" t="n">
-        <v>0.02573334031930896</v>
+        <v>0.01271697068135724</v>
       </c>
       <c r="L861" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="862">
@@ -45532,7 +45532,7 @@
         <v>0</v>
       </c>
       <c r="I881" t="n">
-        <v>122.701</v>
+        <v>122.312</v>
       </c>
       <c r="J881" t="inlineStr">
         <is>
@@ -45540,10 +45540,10 @@
         </is>
       </c>
       <c r="K881" t="n">
-        <v>0.01775879230258792</v>
+        <v>0.01453218314532179</v>
       </c>
       <c r="L881" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="882">
@@ -46556,7 +46556,7 @@
         <v>0</v>
       </c>
       <c r="I901" t="n">
-        <v>94.593</v>
+        <v>94.342</v>
       </c>
       <c r="J901" t="inlineStr">
         <is>
@@ -46564,7 +46564,7 @@
         </is>
       </c>
       <c r="K901" t="n">
-        <v>-0.02278949162697963</v>
+        <v>-0.02538249362080192</v>
       </c>
       <c r="L901" t="n">
         <v>8</v>
@@ -47580,7 +47580,7 @@
         <v>0</v>
       </c>
       <c r="I921" t="n">
-        <v>123.688</v>
+        <v>123.457</v>
       </c>
       <c r="J921" t="inlineStr">
         <is>
@@ -47588,7 +47588,7 @@
         </is>
       </c>
       <c r="K921" t="n">
-        <v>0.0227727520796468</v>
+        <v>0.02086261927993771</v>
       </c>
       <c r="L921" t="n">
         <v>44</v>
@@ -48604,7 +48604,7 @@
         <v>0</v>
       </c>
       <c r="I941" t="n">
-        <v>108.193</v>
+        <v>108.037</v>
       </c>
       <c r="J941" t="inlineStr">
         <is>
@@ -48612,10 +48612,10 @@
         </is>
       </c>
       <c r="K941" t="n">
-        <v>0.009536161834824641</v>
+        <v>0.008080544177062832</v>
       </c>
       <c r="L941" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="942">
@@ -49628,7 +49628,7 @@
         <v>0</v>
       </c>
       <c r="I961" t="n">
-        <v>152.44</v>
+        <v>151.134</v>
       </c>
       <c r="J961" t="inlineStr">
         <is>
@@ -49636,10 +49636,10 @@
         </is>
       </c>
       <c r="K961" t="n">
-        <v>0.03661895209275445</v>
+        <v>0.02773792118595075</v>
       </c>
       <c r="L961" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="962">
@@ -50652,7 +50652,7 @@
         <v>0</v>
       </c>
       <c r="I981" t="n">
-        <v>120.831</v>
+        <v>120.836</v>
       </c>
       <c r="J981" t="inlineStr">
         <is>
@@ -50660,10 +50660,10 @@
         </is>
       </c>
       <c r="K981" t="n">
-        <v>0.05790731677421057</v>
+        <v>0.05795109309472313</v>
       </c>
       <c r="L981" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="982">
@@ -51676,7 +51676,7 @@
         <v>0</v>
       </c>
       <c r="I1001" t="n">
-        <v>100.222</v>
+        <v>104.415</v>
       </c>
       <c r="J1001" t="inlineStr">
         <is>
@@ -51684,10 +51684,10 @@
         </is>
       </c>
       <c r="K1001" t="n">
-        <v>0.06081967907193353</v>
+        <v>0.1052013209704052</v>
       </c>
       <c r="L1001" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="1002">
@@ -52700,7 +52700,7 @@
         <v>0</v>
       </c>
       <c r="I1021" t="n">
-        <v>106.67</v>
+        <v>106.048</v>
       </c>
       <c r="J1021" t="inlineStr">
         <is>
@@ -52708,10 +52708,10 @@
         </is>
       </c>
       <c r="K1021" t="n">
-        <v>0.06064372433405252</v>
+        <v>0.05445903888794978</v>
       </c>
       <c r="L1021" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1022">
@@ -53724,7 +53724,7 @@
         <v>0</v>
       </c>
       <c r="I1041" t="n">
-        <v>122.024</v>
+        <v>121.736</v>
       </c>
       <c r="J1041" t="inlineStr">
         <is>
@@ -53732,10 +53732,10 @@
         </is>
       </c>
       <c r="K1041" t="n">
-        <v>0.005048965909184577</v>
+        <v>0.002676857945326239</v>
       </c>
       <c r="L1041" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1042">
@@ -54748,7 +54748,7 @@
         <v>0</v>
       </c>
       <c r="I1061" t="n">
-        <v>108.694</v>
+        <v>108.7</v>
       </c>
       <c r="J1061" t="inlineStr">
         <is>
@@ -54756,10 +54756,10 @@
         </is>
       </c>
       <c r="K1061" t="n">
-        <v>0.02139695725307056</v>
+        <v>0.02145333922211679</v>
       </c>
       <c r="L1061" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1062">
@@ -55772,7 +55772,7 @@
         <v>0</v>
       </c>
       <c r="I1081" t="n">
-        <v>141.382</v>
+        <v>141.122</v>
       </c>
       <c r="J1081" t="inlineStr">
         <is>
@@ -55780,7 +55780,7 @@
         </is>
       </c>
       <c r="K1081" t="n">
-        <v>0.0366845335425543</v>
+        <v>0.03477808166946539</v>
       </c>
       <c r="L1081" t="n">
         <v>56</v>
@@ -56796,7 +56796,7 @@
         <v>0</v>
       </c>
       <c r="I1101" t="n">
-        <v>123.681</v>
+        <v>123.761</v>
       </c>
       <c r="J1101" t="inlineStr">
         <is>
@@ -56804,10 +56804,10 @@
         </is>
       </c>
       <c r="K1101" t="n">
-        <v>0.00127911401115588</v>
+        <v>0.001926766675032221</v>
       </c>
       <c r="L1101" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1102">
@@ -57820,7 +57820,7 @@
         <v>0</v>
       </c>
       <c r="I1121" t="n">
-        <v>137.337</v>
+        <v>137.375</v>
       </c>
       <c r="J1121" t="inlineStr">
         <is>
@@ -57828,10 +57828,10 @@
         </is>
       </c>
       <c r="K1121" t="n">
-        <v>0.06911986797241121</v>
+        <v>0.06941568450388447</v>
       </c>
       <c r="L1121" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1122">
@@ -58844,7 +58844,7 @@
         <v>0</v>
       </c>
       <c r="I1141" t="n">
-        <v>80.512</v>
+        <v>80.351</v>
       </c>
       <c r="J1141" t="inlineStr">
         <is>
@@ -58852,7 +58852,7 @@
         </is>
       </c>
       <c r="K1141" t="n">
-        <v>-0.01719949707645174</v>
+        <v>-0.01916480511712515</v>
       </c>
       <c r="L1141" t="n">
         <v>9</v>
@@ -59868,7 +59868,7 @@
         <v>0</v>
       </c>
       <c r="I1161" t="n">
-        <v>114.418</v>
+        <v>114.411</v>
       </c>
       <c r="J1161" t="inlineStr">
         <is>
@@ -59876,10 +59876,10 @@
         </is>
       </c>
       <c r="K1161" t="n">
-        <v>0.01398440269408008</v>
+        <v>0.01392236795462609</v>
       </c>
       <c r="L1161" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1162">
@@ -60892,7 +60892,7 @@
         <v>0</v>
       </c>
       <c r="I1181" t="n">
-        <v>122.493</v>
+        <v>122.481</v>
       </c>
       <c r="J1181" t="inlineStr">
         <is>
@@ -60900,10 +60900,10 @@
         </is>
       </c>
       <c r="K1181" t="n">
-        <v>0.0315981842834403</v>
+        <v>0.03149712399255522</v>
       </c>
       <c r="L1181" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1182">
@@ -61916,7 +61916,7 @@
         <v>0</v>
       </c>
       <c r="I1201" t="n">
-        <v>108.377</v>
+        <v>108.382</v>
       </c>
       <c r="J1201" t="inlineStr">
         <is>
@@ -61924,10 +61924,10 @@
         </is>
       </c>
       <c r="K1201" t="n">
-        <v>0.009764369368949755</v>
+        <v>0.009810955100671981</v>
       </c>
       <c r="L1201" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1202">
@@ -62940,7 +62940,7 @@
         <v>0</v>
       </c>
       <c r="I1221" t="n">
-        <v>145.746</v>
+        <v>145.725</v>
       </c>
       <c r="J1221" t="inlineStr">
         <is>
@@ -62948,10 +62948,10 @@
         </is>
       </c>
       <c r="K1221" t="n">
-        <v>0.04276341678054507</v>
+        <v>0.04261316887149502</v>
       </c>
       <c r="L1221" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1222">
@@ -63964,7 +63964,7 @@
         <v>0</v>
       </c>
       <c r="I1241" t="n">
-        <v>134.311</v>
+        <v>133.656</v>
       </c>
       <c r="J1241" t="inlineStr">
         <is>
@@ -63972,10 +63972,10 @@
         </is>
       </c>
       <c r="K1241" t="n">
-        <v>0.06745136063072232</v>
+        <v>0.06224567650050861</v>
       </c>
       <c r="L1241" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1242">
@@ -64988,7 +64988,7 @@
         <v>0</v>
       </c>
       <c r="I1261" t="n">
-        <v>118.811</v>
+        <v>119.208</v>
       </c>
       <c r="J1261" t="inlineStr">
         <is>
@@ -64996,10 +64996,10 @@
         </is>
       </c>
       <c r="K1261" t="n">
-        <v>0.00137381161081529</v>
+        <v>0.00471984357089883</v>
       </c>
       <c r="L1261" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1262">
@@ -66012,7 +66012,7 @@
         <v>0</v>
       </c>
       <c r="I1281" t="n">
-        <v>150.512</v>
+        <v>151.538</v>
       </c>
       <c r="J1281" t="inlineStr">
         <is>
@@ -66020,10 +66020,10 @@
         </is>
       </c>
       <c r="K1281" t="n">
-        <v>0.07703206508905369</v>
+        <v>0.08437390426985902</v>
       </c>
       <c r="L1281" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1282">
@@ -67036,7 +67036,7 @@
         <v>0</v>
       </c>
       <c r="I1301" t="n">
-        <v>110.813</v>
+        <v>111.282</v>
       </c>
       <c r="J1301" t="inlineStr">
         <is>
@@ -67044,10 +67044,10 @@
         </is>
       </c>
       <c r="K1301" t="n">
-        <v>0.0451788762815617</v>
+        <v>0.0496024447525536</v>
       </c>
       <c r="L1301" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1302">
@@ -68060,7 +68060,7 @@
         <v>0</v>
       </c>
       <c r="I1321" t="n">
-        <v>86.19199999999999</v>
+        <v>83.983</v>
       </c>
       <c r="J1321" t="inlineStr">
         <is>
@@ -68068,10 +68068,10 @@
         </is>
       </c>
       <c r="K1321" t="n">
-        <v>-0.02965347983698463</v>
+        <v>-0.05452232454461525</v>
       </c>
       <c r="L1321" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1322">
@@ -69084,7 +69084,7 @@
         <v>0</v>
       </c>
       <c r="I1341" t="n">
-        <v>164.326</v>
+        <v>163.433</v>
       </c>
       <c r="J1341" t="inlineStr">
         <is>
@@ -69092,10 +69092,10 @@
         </is>
       </c>
       <c r="K1341" t="n">
-        <v>0.1101457891394522</v>
+        <v>0.1041129021361689</v>
       </c>
       <c r="L1341" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1342">
@@ -70108,7 +70108,7 @@
         <v>0</v>
       </c>
       <c r="I1361" t="n">
-        <v>141.632</v>
+        <v>140.397</v>
       </c>
       <c r="J1361" t="inlineStr">
         <is>
@@ -70116,10 +70116,10 @@
         </is>
       </c>
       <c r="K1361" t="n">
-        <v>0.083086711479196</v>
+        <v>0.07364243272385229</v>
       </c>
       <c r="L1361" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1362">
@@ -71132,7 +71132,7 @@
         <v>0</v>
       </c>
       <c r="I1381" t="n">
-        <v>180.272</v>
+        <v>179.546</v>
       </c>
       <c r="J1381" t="inlineStr">
         <is>
@@ -71140,10 +71140,10 @@
         </is>
       </c>
       <c r="K1381" t="n">
-        <v>0.05628537611475037</v>
+        <v>0.05203145324786429</v>
       </c>
       <c r="L1381" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1382">
@@ -72156,7 +72156,7 @@
         <v>0</v>
       </c>
       <c r="I1401" t="n">
-        <v>116.3</v>
+        <v>116.648</v>
       </c>
       <c r="J1401" t="inlineStr">
         <is>
@@ -72164,10 +72164,10 @@
         </is>
       </c>
       <c r="K1401" t="n">
-        <v>0.02923997309639281</v>
+        <v>0.03231972813196937</v>
       </c>
       <c r="L1401" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1402">
@@ -73180,7 +73180,7 @@
         <v>0</v>
       </c>
       <c r="I1421" t="n">
-        <v>118.298</v>
+        <v>118.344</v>
       </c>
       <c r="J1421" t="inlineStr">
         <is>
@@ -73188,10 +73188,10 @@
         </is>
       </c>
       <c r="K1421" t="n">
-        <v>0.03031781008038892</v>
+        <v>0.03071844761664222</v>
       </c>
       <c r="L1421" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1422">
@@ -74204,7 +74204,7 @@
         <v>0</v>
       </c>
       <c r="I1441" t="n">
-        <v>127.862</v>
+        <v>128.392</v>
       </c>
       <c r="J1441" t="inlineStr">
         <is>
@@ -74212,10 +74212,10 @@
         </is>
       </c>
       <c r="K1441" t="n">
-        <v>0.01198277772501344</v>
+        <v>0.01617754139361116</v>
       </c>
       <c r="L1441" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1442">
@@ -75228,7 +75228,7 @@
         <v>0</v>
       </c>
       <c r="I1461" t="n">
-        <v>184.073</v>
+        <v>183.834</v>
       </c>
       <c r="J1461" t="inlineStr">
         <is>
@@ -75236,10 +75236,10 @@
         </is>
       </c>
       <c r="K1461" t="n">
-        <v>0.05299498309583606</v>
+        <v>0.05162777660189133</v>
       </c>
       <c r="L1461" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1462">
@@ -76252,7 +76252,7 @@
         <v>0</v>
       </c>
       <c r="I1481" t="n">
-        <v>146.019</v>
+        <v>145.612</v>
       </c>
       <c r="J1481" t="inlineStr">
         <is>
@@ -76260,10 +76260,10 @@
         </is>
       </c>
       <c r="K1481" t="n">
-        <v>0.04371600323080993</v>
+        <v>0.04080684474242879</v>
       </c>
       <c r="L1481" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1482">
@@ -77276,7 +77276,7 @@
         <v>0</v>
       </c>
       <c r="I1501" t="n">
-        <v>341.708</v>
+        <v>334.619</v>
       </c>
       <c r="J1501" t="inlineStr">
         <is>
@@ -77284,7 +77284,7 @@
         </is>
       </c>
       <c r="K1501" t="n">
-        <v>0.1411796923529058</v>
+        <v>0.1175050261493351</v>
       </c>
       <c r="L1501" t="n">
         <v>90</v>
@@ -78300,7 +78300,7 @@
         <v>0</v>
       </c>
       <c r="I1521" t="n">
-        <v>137.144</v>
+        <v>139.276</v>
       </c>
       <c r="J1521" t="inlineStr">
         <is>
@@ -78308,10 +78308,10 @@
         </is>
       </c>
       <c r="K1521" t="n">
-        <v>-0.003248759003132484</v>
+        <v>0.0122464405375351</v>
       </c>
       <c r="L1521" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1522">
@@ -79324,7 +79324,7 @@
         <v>0</v>
       </c>
       <c r="I1541" t="n">
-        <v>110.252</v>
+        <v>109.933</v>
       </c>
       <c r="J1541" t="inlineStr">
         <is>
@@ -79332,10 +79332,10 @@
         </is>
       </c>
       <c r="K1541" t="n">
-        <v>0.02200634049574512</v>
+        <v>0.01904929642744579</v>
       </c>
       <c r="L1541" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1542">
@@ -80348,7 +80348,7 @@
         <v>0</v>
       </c>
       <c r="I1561" t="n">
-        <v>112.84</v>
+        <v>112.833</v>
       </c>
       <c r="J1561" t="inlineStr">
         <is>
@@ -80356,7 +80356,7 @@
         </is>
       </c>
       <c r="K1561" t="n">
-        <v>0.009835244001754173</v>
+        <v>0.009772599135500881</v>
       </c>
       <c r="L1561" t="n">
         <v>30</v>
@@ -81372,7 +81372,7 @@
         <v>0</v>
       </c>
       <c r="I1581" t="n">
-        <v>113.383</v>
+        <v>113.25</v>
       </c>
       <c r="J1581" t="inlineStr">
         <is>
@@ -81380,7 +81380,7 @@
         </is>
       </c>
       <c r="K1581" t="n">
-        <v>0.01858706002838817</v>
+        <v>0.01739224176653442</v>
       </c>
       <c r="L1581" t="n">
         <v>41</v>
@@ -82407,7 +82407,7 @@
         <v>0.007241472030857343</v>
       </c>
       <c r="L1601" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1602">
@@ -83420,7 +83420,7 @@
         <v>0</v>
       </c>
       <c r="I1621" t="n">
-        <v>63.889</v>
+        <v>64.392</v>
       </c>
       <c r="J1621" t="inlineStr">
         <is>
@@ -83428,7 +83428,7 @@
         </is>
       </c>
       <c r="K1621" t="n">
-        <v>-0.1004843296820882</v>
+        <v>-0.09340241601666999</v>
       </c>
       <c r="L1621" t="n">
         <v>1</v>
@@ -84444,7 +84444,7 @@
         <v>0</v>
       </c>
       <c r="I1641" t="n">
-        <v>127.407</v>
+        <v>127.388</v>
       </c>
       <c r="J1641" t="inlineStr">
         <is>
@@ -84452,10 +84452,10 @@
         </is>
       </c>
       <c r="K1641" t="n">
-        <v>0.05162067798568737</v>
+        <v>0.05146385149356592</v>
       </c>
       <c r="L1641" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1642">
@@ -85468,7 +85468,7 @@
         <v>0</v>
       </c>
       <c r="I1661" t="n">
-        <v>182.268</v>
+        <v>181.517</v>
       </c>
       <c r="J1661" t="inlineStr">
         <is>
@@ -85476,10 +85476,10 @@
         </is>
       </c>
       <c r="K1661" t="n">
-        <v>0.09766276625855919</v>
+        <v>0.09314005937934744</v>
       </c>
       <c r="L1661" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1662">
@@ -86492,7 +86492,7 @@
         <v>0</v>
       </c>
       <c r="I1681" t="n">
-        <v>105.088</v>
+        <v>104.387</v>
       </c>
       <c r="J1681" t="inlineStr">
         <is>
@@ -86500,10 +86500,10 @@
         </is>
       </c>
       <c r="K1681" t="n">
-        <v>0.00628159950972873</v>
+        <v>-0.0004309024053930077</v>
       </c>
       <c r="L1681" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1682">
@@ -87516,7 +87516,7 @@
         <v>0</v>
       </c>
       <c r="I1701" t="n">
-        <v>274.769</v>
+        <v>273.157</v>
       </c>
       <c r="J1701" t="inlineStr">
         <is>
@@ -87524,10 +87524,10 @@
         </is>
       </c>
       <c r="K1701" t="n">
-        <v>0.07403382728306807</v>
+        <v>0.06773274335591339</v>
       </c>
       <c r="L1701" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1702">
@@ -88540,7 +88540,7 @@
         <v>0</v>
       </c>
       <c r="I1721" t="n">
-        <v>149.419</v>
+        <v>148.736</v>
       </c>
       <c r="J1721" t="inlineStr">
         <is>
@@ -88548,10 +88548,10 @@
         </is>
       </c>
       <c r="K1721" t="n">
-        <v>0.09318710583690626</v>
+        <v>0.08819010550035844</v>
       </c>
       <c r="L1721" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1722">
@@ -89564,7 +89564,7 @@
         <v>0</v>
       </c>
       <c r="I1741" t="n">
-        <v>102.875</v>
+        <v>102.574</v>
       </c>
       <c r="J1741" t="inlineStr">
         <is>
@@ -89572,7 +89572,7 @@
         </is>
       </c>
       <c r="K1741" t="n">
-        <v>-0.0250755773732243</v>
+        <v>-0.02792809014319431</v>
       </c>
       <c r="L1741" t="n">
         <v>7</v>
@@ -90588,7 +90588,7 @@
         <v>0</v>
       </c>
       <c r="I1761" t="n">
-        <v>195.784</v>
+        <v>195.706</v>
       </c>
       <c r="J1761" t="inlineStr">
         <is>
@@ -90596,7 +90596,7 @@
         </is>
       </c>
       <c r="K1761" t="n">
-        <v>0.1417108401415883</v>
+        <v>0.141255984558236</v>
       </c>
       <c r="L1761" t="n">
         <v>91</v>
@@ -91612,7 +91612,7 @@
         <v>0</v>
       </c>
       <c r="I1781" t="n">
-        <v>137.402</v>
+        <v>136.187</v>
       </c>
       <c r="J1781" t="inlineStr">
         <is>
@@ -91620,10 +91620,10 @@
         </is>
       </c>
       <c r="K1781" t="n">
-        <v>0.03160850501531609</v>
+        <v>0.0224863355156466</v>
       </c>
       <c r="L1781" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1782">
@@ -92636,7 +92636,7 @@
         <v>0</v>
       </c>
       <c r="I1801" t="n">
-        <v>125.165</v>
+        <v>124.665</v>
       </c>
       <c r="J1801" t="inlineStr">
         <is>
@@ -92644,10 +92644,10 @@
         </is>
       </c>
       <c r="K1801" t="n">
-        <v>0.04122819422838564</v>
+        <v>0.03706877188896018</v>
       </c>
       <c r="L1801" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1802">
@@ -93660,7 +93660,7 @@
         <v>0</v>
       </c>
       <c r="I1821" t="n">
-        <v>103.227</v>
+        <v>103.729</v>
       </c>
       <c r="J1821" t="inlineStr">
         <is>
@@ -93668,10 +93668,10 @@
         </is>
       </c>
       <c r="K1821" t="n">
-        <v>0.01731546269833451</v>
+        <v>0.02226273775500154</v>
       </c>
       <c r="L1821" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1822">
@@ -94271,7 +94271,7 @@
         <v>0</v>
       </c>
       <c r="L1841" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/01_macro_economic/PCE/Z.economic_pulse_monthly/pce_real_detail.xlsx
+++ b/01_macro_economic/PCE/Z.economic_pulse_monthly/pce_real_detail.xlsx
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>114.648</v>
+        <v>112.624</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0.008142663688644358</v>
+        <v>-0.009655123898629991</v>
       </c>
       <c r="L22" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -2628,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>161.992</v>
+        <v>161.604</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.04627070039011016</v>
+        <v>0.04376469372464942</v>
       </c>
       <c r="L43" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44">
@@ -3704,7 +3704,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>134.596</v>
+        <v>134.535</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>0.01349356947079916</v>
+        <v>0.01303424595644698</v>
       </c>
       <c r="L64" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65">
@@ -4780,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>131.788</v>
+        <v>131.803</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4788,10 +4788,10 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>0.06542705849064245</v>
+        <v>0.06554832450786208</v>
       </c>
       <c r="L85" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86">
@@ -5856,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>96.962</v>
+        <v>95.663</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>-0.03875246602095739</v>
+        <v>-0.0516303000862488</v>
       </c>
       <c r="L106" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -6932,7 +6932,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>111.376</v>
+        <v>111.772</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -6940,10 +6940,10 @@
         </is>
       </c>
       <c r="K127" t="n">
-        <v>0.06466815153282157</v>
+        <v>0.06845360430547465</v>
       </c>
       <c r="L127" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="128">
@@ -8008,7 +8008,7 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>136.072</v>
+        <v>135.546</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>0.05074903474903469</v>
+        <v>0.04668725868725865</v>
       </c>
       <c r="L148" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="149">
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>114.693</v>
+        <v>114.876</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -9092,10 +9092,10 @@
         </is>
       </c>
       <c r="K169" t="n">
-        <v>0.02997620223609165</v>
+        <v>0.03161959498899924</v>
       </c>
       <c r="L169" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="170">
@@ -10160,7 +10160,7 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>148.483</v>
+        <v>148.342</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -10168,10 +10168,10 @@
         </is>
       </c>
       <c r="K190" t="n">
-        <v>0.05347438025910645</v>
+        <v>0.05247399713365408</v>
       </c>
       <c r="L190" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="191">
@@ -11236,7 +11236,7 @@
         <v>0</v>
       </c>
       <c r="I211" t="n">
-        <v>96.63500000000001</v>
+        <v>96.414</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="K211" t="n">
-        <v>-0.05631725942852672</v>
+        <v>-0.05847542040194531</v>
       </c>
       <c r="L211" t="n">
         <v>2</v>
@@ -12312,7 +12312,7 @@
         <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>112.927</v>
+        <v>111.367</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -12320,10 +12320,10 @@
         </is>
       </c>
       <c r="K232" t="n">
-        <v>0.05925335334396409</v>
+        <v>0.04462057968295663</v>
       </c>
       <c r="L232" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="233">
@@ -13388,7 +13388,7 @@
         <v>0</v>
       </c>
       <c r="I253" t="n">
-        <v>111.4</v>
+        <v>110.713</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -13396,10 +13396,10 @@
         </is>
       </c>
       <c r="K253" t="n">
-        <v>0.05891522974848384</v>
+        <v>0.05238493564761115</v>
       </c>
       <c r="L253" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="254">
@@ -14475,7 +14475,7 @@
         <v>-0.003832808843702185</v>
       </c>
       <c r="L274" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="275">
@@ -15540,7 +15540,7 @@
         <v>0</v>
       </c>
       <c r="I295" t="n">
-        <v>131.712</v>
+        <v>133.434</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -15548,10 +15548,10 @@
         </is>
       </c>
       <c r="K295" t="n">
-        <v>-0.05297670405522015</v>
+        <v>-0.0405953408110441</v>
       </c>
       <c r="L295" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="296">
@@ -16616,7 +16616,7 @@
         <v>0</v>
       </c>
       <c r="I316" t="n">
-        <v>139.485</v>
+        <v>139.341</v>
       </c>
       <c r="J316" t="inlineStr">
         <is>
@@ -16624,10 +16624,10 @@
         </is>
       </c>
       <c r="K316" t="n">
-        <v>0.05464319738692569</v>
+        <v>0.05355441636800795</v>
       </c>
       <c r="L316" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="317">
@@ -17703,7 +17703,7 @@
         <v>0.01089576870901121</v>
       </c>
       <c r="L337" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="338">
@@ -18768,7 +18768,7 @@
         <v>0</v>
       </c>
       <c r="I358" t="n">
-        <v>109.883</v>
+        <v>109.432</v>
       </c>
       <c r="J358" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         </is>
       </c>
       <c r="K358" t="n">
-        <v>0.02404406214178545</v>
+        <v>0.01984101096893842</v>
       </c>
       <c r="L358" t="n">
         <v>36</v>
@@ -19844,7 +19844,7 @@
         <v>0</v>
       </c>
       <c r="I379" t="n">
-        <v>107.029</v>
+        <v>107.037</v>
       </c>
       <c r="J379" t="inlineStr">
         <is>
@@ -19852,10 +19852,10 @@
         </is>
       </c>
       <c r="K379" t="n">
-        <v>0.0327595190767509</v>
+        <v>0.03283671381978892</v>
       </c>
       <c r="L379" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="380">
@@ -20920,7 +20920,7 @@
         <v>0</v>
       </c>
       <c r="I400" t="n">
-        <v>117.651</v>
+        <v>118.452</v>
       </c>
       <c r="J400" t="inlineStr">
         <is>
@@ -20928,10 +20928,10 @@
         </is>
       </c>
       <c r="K400" t="n">
-        <v>0.004010889137317397</v>
+        <v>0.0108464682841074</v>
       </c>
       <c r="L400" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="401">
@@ -21996,7 +21996,7 @@
         <v>0</v>
       </c>
       <c r="I421" t="n">
-        <v>181.406</v>
+        <v>181.042</v>
       </c>
       <c r="J421" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         </is>
       </c>
       <c r="K421" t="n">
-        <v>0.1195206092360481</v>
+        <v>0.1172742364492501</v>
       </c>
       <c r="L421" t="n">
         <v>90</v>
@@ -23072,7 +23072,7 @@
         <v>0</v>
       </c>
       <c r="I442" t="n">
-        <v>94.506</v>
+        <v>95.608</v>
       </c>
       <c r="J442" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         </is>
       </c>
       <c r="K442" t="n">
-        <v>0.1665103189493433</v>
+        <v>0.1801125703564728</v>
       </c>
       <c r="L442" t="n">
         <v>92</v>
@@ -24148,7 +24148,7 @@
         <v>0</v>
       </c>
       <c r="I463" t="n">
-        <v>118.5</v>
+        <v>117.805</v>
       </c>
       <c r="J463" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         </is>
       </c>
       <c r="K463" t="n">
-        <v>0.07772341160849083</v>
+        <v>0.07140258653618803</v>
       </c>
       <c r="L463" t="n">
         <v>84</v>
@@ -25224,7 +25224,7 @@
         <v>0</v>
       </c>
       <c r="I484" t="n">
-        <v>130.111</v>
+        <v>130.244</v>
       </c>
       <c r="J484" t="inlineStr">
         <is>
@@ -25232,10 +25232,10 @@
         </is>
       </c>
       <c r="K484" t="n">
-        <v>0.02852919321433656</v>
+        <v>0.0295805599911465</v>
       </c>
       <c r="L484" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="485">
@@ -26300,7 +26300,7 @@
         <v>0</v>
       </c>
       <c r="I505" t="n">
-        <v>132.173</v>
+        <v>132.023</v>
       </c>
       <c r="J505" t="inlineStr">
         <is>
@@ -26308,10 +26308,10 @@
         </is>
       </c>
       <c r="K505" t="n">
-        <v>0.03815732631661639</v>
+        <v>0.03697914621215093</v>
       </c>
       <c r="L505" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="506">
@@ -27376,7 +27376,7 @@
         <v>0</v>
       </c>
       <c r="I526" t="n">
-        <v>105.711</v>
+        <v>108.144</v>
       </c>
       <c r="J526" t="inlineStr">
         <is>
@@ -27384,10 +27384,10 @@
         </is>
       </c>
       <c r="K526" t="n">
-        <v>0.05664507616648673</v>
+        <v>0.08096437567470316</v>
       </c>
       <c r="L526" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="527">
@@ -28452,7 +28452,7 @@
         <v>0</v>
       </c>
       <c r="I547" t="n">
-        <v>176.132</v>
+        <v>176.112</v>
       </c>
       <c r="J547" t="inlineStr">
         <is>
@@ -28460,10 +28460,10 @@
         </is>
       </c>
       <c r="K547" t="n">
-        <v>0.1045182328410623</v>
+        <v>0.1043928134700405</v>
       </c>
       <c r="L547" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="548">
@@ -29539,7 +29539,7 @@
         <v>0.008302638128422135</v>
       </c>
       <c r="L568" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="569">
@@ -30604,7 +30604,7 @@
         <v>0</v>
       </c>
       <c r="I589" t="n">
-        <v>99.76600000000001</v>
+        <v>99.74299999999999</v>
       </c>
       <c r="J589" t="inlineStr">
         <is>
@@ -30612,10 +30612,10 @@
         </is>
       </c>
       <c r="K589" t="n">
-        <v>-0.008999523204068605</v>
+        <v>-0.009227987921169745</v>
       </c>
       <c r="L589" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="590">
@@ -31680,7 +31680,7 @@
         <v>0</v>
       </c>
       <c r="I610" t="n">
-        <v>104.356</v>
+        <v>104.165</v>
       </c>
       <c r="J610" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         </is>
       </c>
       <c r="K610" t="n">
-        <v>-0.004891817410292876</v>
+        <v>-0.006713137342780007</v>
       </c>
       <c r="L610" t="n">
         <v>11</v>
@@ -32756,7 +32756,7 @@
         <v>0</v>
       </c>
       <c r="I631" t="n">
-        <v>109.358</v>
+        <v>109.306</v>
       </c>
       <c r="J631" t="inlineStr">
         <is>
@@ -32764,10 +32764,10 @@
         </is>
       </c>
       <c r="K631" t="n">
-        <v>0.0148763398450189</v>
+        <v>0.01439376363045808</v>
       </c>
       <c r="L631" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="632">
@@ -33832,7 +33832,7 @@
         <v>0</v>
       </c>
       <c r="I652" t="n">
-        <v>128.933</v>
+        <v>128.563</v>
       </c>
       <c r="J652" t="inlineStr">
         <is>
@@ -33840,10 +33840,10 @@
         </is>
       </c>
       <c r="K652" t="n">
-        <v>0.03800759990983149</v>
+        <v>0.03502882169194588</v>
       </c>
       <c r="L652" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="653">
@@ -34908,7 +34908,7 @@
         <v>0</v>
       </c>
       <c r="I673" t="n">
-        <v>121.019</v>
+        <v>120.989</v>
       </c>
       <c r="J673" t="inlineStr">
         <is>
@@ -34916,10 +34916,10 @@
         </is>
       </c>
       <c r="K673" t="n">
-        <v>0.03471301909216051</v>
+        <v>0.03445651895108548</v>
       </c>
       <c r="L673" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="674">
@@ -35984,7 +35984,7 @@
         <v>0</v>
       </c>
       <c r="I694" t="n">
-        <v>114.24</v>
+        <v>114.241</v>
       </c>
       <c r="J694" t="inlineStr">
         <is>
@@ -35992,10 +35992,10 @@
         </is>
       </c>
       <c r="K694" t="n">
-        <v>0.01334090263979548</v>
+        <v>0.01334977292080608</v>
       </c>
       <c r="L694" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="695">
@@ -37060,7 +37060,7 @@
         <v>0</v>
       </c>
       <c r="I715" t="n">
-        <v>123.275</v>
+        <v>123.365</v>
       </c>
       <c r="J715" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         </is>
       </c>
       <c r="K715" t="n">
-        <v>0.03071018879282961</v>
+        <v>0.03146268457049195</v>
       </c>
       <c r="L715" t="n">
         <v>49</v>
@@ -38136,7 +38136,7 @@
         <v>0</v>
       </c>
       <c r="I736" t="n">
-        <v>110.873</v>
+        <v>109.933</v>
       </c>
       <c r="J736" t="inlineStr">
         <is>
@@ -38144,10 +38144,10 @@
         </is>
       </c>
       <c r="K736" t="n">
-        <v>0.05923208468277408</v>
+        <v>0.05025173635990177</v>
       </c>
       <c r="L736" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="737">
@@ -39212,7 +39212,7 @@
         <v>0</v>
       </c>
       <c r="I757" t="n">
-        <v>109.469</v>
+        <v>109.426</v>
       </c>
       <c r="J757" t="inlineStr">
         <is>
@@ -39220,10 +39220,10 @@
         </is>
       </c>
       <c r="K757" t="n">
-        <v>0.01356431243287282</v>
+        <v>0.01316617903040629</v>
       </c>
       <c r="L757" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="758">
@@ -40288,7 +40288,7 @@
         <v>0</v>
       </c>
       <c r="I778" t="n">
-        <v>135.801</v>
+        <v>132.58</v>
       </c>
       <c r="J778" t="inlineStr">
         <is>
@@ -40296,10 +40296,10 @@
         </is>
       </c>
       <c r="K778" t="n">
-        <v>0.08361660362905154</v>
+        <v>0.05791481144571597</v>
       </c>
       <c r="L778" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="779">
@@ -41364,7 +41364,7 @@
         <v>0</v>
       </c>
       <c r="I799" t="n">
-        <v>136.011</v>
+        <v>136.066</v>
       </c>
       <c r="J799" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         </is>
       </c>
       <c r="K799" t="n">
-        <v>-0.04883421682028621</v>
+        <v>-0.04844958529728516</v>
       </c>
       <c r="L799" t="n">
         <v>4</v>
@@ -42440,7 +42440,7 @@
         <v>0</v>
       </c>
       <c r="I820" t="n">
-        <v>108.988</v>
+        <v>108.922</v>
       </c>
       <c r="J820" t="inlineStr">
         <is>
@@ -42448,10 +42448,10 @@
         </is>
       </c>
       <c r="K820" t="n">
-        <v>0.009606210225009626</v>
+        <v>0.008994821724671365</v>
       </c>
       <c r="L820" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="821">
@@ -43516,7 +43516,7 @@
         <v>0</v>
       </c>
       <c r="I841" t="n">
-        <v>142.172</v>
+        <v>143.706</v>
       </c>
       <c r="J841" t="inlineStr">
         <is>
@@ -43524,10 +43524,10 @@
         </is>
       </c>
       <c r="K841" t="n">
-        <v>0.03425649083753446</v>
+        <v>0.04541585735797993</v>
       </c>
       <c r="L841" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
     </row>
     <row r="842">
@@ -44592,7 +44592,7 @@
         <v>0</v>
       </c>
       <c r="I862" t="n">
-        <v>119.935</v>
+        <v>119.477</v>
       </c>
       <c r="J862" t="inlineStr">
         <is>
@@ -44600,10 +44600,10 @@
         </is>
       </c>
       <c r="K862" t="n">
-        <v>0.02128837229105462</v>
+        <v>0.01738834248733334</v>
       </c>
       <c r="L862" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="863">
@@ -45668,7 +45668,7 @@
         <v>0</v>
       </c>
       <c r="I883" t="n">
-        <v>99.39100000000001</v>
+        <v>99.28400000000001</v>
       </c>
       <c r="J883" t="inlineStr">
         <is>
@@ -45676,10 +45676,10 @@
         </is>
       </c>
       <c r="K883" t="n">
-        <v>0.02533656573992893</v>
+        <v>0.02423273327487485</v>
       </c>
       <c r="L883" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="884">
@@ -46744,7 +46744,7 @@
         <v>0</v>
       </c>
       <c r="I904" t="n">
-        <v>131.863</v>
+        <v>131.539</v>
       </c>
       <c r="J904" t="inlineStr">
         <is>
@@ -46752,7 +46752,7 @@
         </is>
       </c>
       <c r="K904" t="n">
-        <v>-0.02831857102854696</v>
+        <v>-0.03070608521362361</v>
       </c>
       <c r="L904" t="n">
         <v>7</v>
@@ -47820,7 +47820,7 @@
         <v>0</v>
       </c>
       <c r="I925" t="n">
-        <v>124.206</v>
+        <v>123.434</v>
       </c>
       <c r="J925" t="inlineStr">
         <is>
@@ -47828,10 +47828,10 @@
         </is>
       </c>
       <c r="K925" t="n">
-        <v>0.03512763457259305</v>
+        <v>0.02869381870306942</v>
       </c>
       <c r="L925" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="926">
@@ -48896,7 +48896,7 @@
         <v>0</v>
       </c>
       <c r="I946" t="n">
-        <v>96.681</v>
+        <v>96.92100000000001</v>
       </c>
       <c r="J946" t="inlineStr">
         <is>
@@ -48904,10 +48904,10 @@
         </is>
       </c>
       <c r="K946" t="n">
-        <v>0.0299676140963907</v>
+        <v>0.03252439596028478</v>
       </c>
       <c r="L946" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="947">
@@ -49972,7 +49972,7 @@
         <v>0</v>
       </c>
       <c r="I967" t="n">
-        <v>124.314</v>
+        <v>124.161</v>
       </c>
       <c r="J967" t="inlineStr">
         <is>
@@ -49980,10 +49980,10 @@
         </is>
       </c>
       <c r="K967" t="n">
-        <v>0.03012976681748114</v>
+        <v>0.02886193009496352</v>
       </c>
       <c r="L967" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="968">
@@ -51048,7 +51048,7 @@
         <v>0</v>
       </c>
       <c r="I988" t="n">
-        <v>108.817</v>
+        <v>109.045</v>
       </c>
       <c r="J988" t="inlineStr">
         <is>
@@ -51056,10 +51056,10 @@
         </is>
       </c>
       <c r="K988" t="n">
-        <v>0.01583256317622128</v>
+        <v>0.01796099737679824</v>
       </c>
       <c r="L988" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="989">
@@ -52124,7 +52124,7 @@
         <v>0</v>
       </c>
       <c r="I1009" t="n">
-        <v>150.745</v>
+        <v>150.56</v>
       </c>
       <c r="J1009" t="inlineStr">
         <is>
@@ -52132,10 +52132,10 @@
         </is>
       </c>
       <c r="K1009" t="n">
-        <v>0.01590457256461253</v>
+        <v>0.01465781581696279</v>
       </c>
       <c r="L1009" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1010">
@@ -53200,7 +53200,7 @@
         <v>0</v>
       </c>
       <c r="I1030" t="n">
-        <v>118.741</v>
+        <v>118.932</v>
       </c>
       <c r="J1030" t="inlineStr">
         <is>
@@ -53208,10 +53208,10 @@
         </is>
       </c>
       <c r="K1030" t="n">
-        <v>0.06825665293196836</v>
+        <v>0.06997498965399362</v>
       </c>
       <c r="L1030" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1031">
@@ -54276,7 +54276,7 @@
         <v>0</v>
       </c>
       <c r="I1051" t="n">
-        <v>96.976</v>
+        <v>96.973</v>
       </c>
       <c r="J1051" t="inlineStr">
         <is>
@@ -54284,7 +54284,7 @@
         </is>
       </c>
       <c r="K1051" t="n">
-        <v>0.04203558841227539</v>
+        <v>0.04200335253159126</v>
       </c>
       <c r="L1051" t="n">
         <v>61</v>
@@ -55352,7 +55352,7 @@
         <v>0</v>
       </c>
       <c r="I1072" t="n">
-        <v>108.71</v>
+        <v>108.053</v>
       </c>
       <c r="J1072" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         </is>
       </c>
       <c r="K1072" t="n">
-        <v>0.05908714501436996</v>
+        <v>0.05268644356763597</v>
       </c>
       <c r="L1072" t="n">
         <v>72</v>
@@ -56428,7 +56428,7 @@
         <v>0</v>
       </c>
       <c r="I1093" t="n">
-        <v>122.77</v>
+        <v>122.426</v>
       </c>
       <c r="J1093" t="inlineStr">
         <is>
@@ -56436,10 +56436,10 @@
         </is>
       </c>
       <c r="K1093" t="n">
-        <v>0.0149048914166674</v>
+        <v>0.01206114064166264</v>
       </c>
       <c r="L1093" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1094">
@@ -57504,7 +57504,7 @@
         <v>0</v>
       </c>
       <c r="I1114" t="n">
-        <v>107.575</v>
+        <v>107.692</v>
       </c>
       <c r="J1114" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         </is>
       </c>
       <c r="K1114" t="n">
-        <v>-0.01556608953475602</v>
+        <v>-0.01449540612760358</v>
       </c>
       <c r="L1114" t="n">
         <v>8</v>
@@ -58580,7 +58580,7 @@
         <v>0</v>
       </c>
       <c r="I1135" t="n">
-        <v>142.721</v>
+        <v>142.018</v>
       </c>
       <c r="J1135" t="inlineStr">
         <is>
@@ -58588,10 +58588,10 @@
         </is>
       </c>
       <c r="K1135" t="n">
-        <v>0.04597355769230771</v>
+        <v>0.0408214118198873</v>
       </c>
       <c r="L1135" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1136">
@@ -59656,7 +59656,7 @@
         <v>0</v>
       </c>
       <c r="I1156" t="n">
-        <v>124.703</v>
+        <v>125.058</v>
       </c>
       <c r="J1156" t="inlineStr">
         <is>
@@ -59664,10 +59664,10 @@
         </is>
       </c>
       <c r="K1156" t="n">
-        <v>0.01454663792051414</v>
+        <v>0.01743481267542601</v>
       </c>
       <c r="L1156" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1157">
@@ -60732,7 +60732,7 @@
         <v>0</v>
       </c>
       <c r="I1177" t="n">
-        <v>139.048</v>
+        <v>138.518</v>
       </c>
       <c r="J1177" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         </is>
       </c>
       <c r="K1177" t="n">
-        <v>0.06205937841326592</v>
+        <v>0.05801119742138505</v>
       </c>
       <c r="L1177" t="n">
         <v>77</v>
@@ -61808,7 +61808,7 @@
         <v>0</v>
       </c>
       <c r="I1198" t="n">
-        <v>82.17</v>
+        <v>82.88</v>
       </c>
       <c r="J1198" t="inlineStr">
         <is>
@@ -61816,10 +61816,10 @@
         </is>
       </c>
       <c r="K1198" t="n">
-        <v>0.01739614932210731</v>
+        <v>0.02618708599021846</v>
       </c>
       <c r="L1198" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1199">
@@ -62884,7 +62884,7 @@
         <v>0</v>
       </c>
       <c r="I1219" t="n">
-        <v>114.83</v>
+        <v>114.832</v>
       </c>
       <c r="J1219" t="inlineStr">
         <is>
@@ -62892,10 +62892,10 @@
         </is>
       </c>
       <c r="K1219" t="n">
-        <v>0.01480270425522501</v>
+        <v>0.01482037912597756</v>
       </c>
       <c r="L1219" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1220">
@@ -63960,7 +63960,7 @@
         <v>0</v>
       </c>
       <c r="I1240" t="n">
-        <v>122.986</v>
+        <v>122.801</v>
       </c>
       <c r="J1240" t="inlineStr">
         <is>
@@ -63968,10 +63968,10 @@
         </is>
       </c>
       <c r="K1240" t="n">
-        <v>0.03081913351046439</v>
+        <v>0.0292685379979718</v>
       </c>
       <c r="L1240" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1241">
@@ -65036,7 +65036,7 @@
         <v>0</v>
       </c>
       <c r="I1261" t="n">
-        <v>108.042</v>
+        <v>108.143</v>
       </c>
       <c r="J1261" t="inlineStr">
         <is>
@@ -65044,10 +65044,10 @@
         </is>
       </c>
       <c r="K1261" t="n">
-        <v>-0.00609907547950872</v>
+        <v>-0.005169955383837022</v>
       </c>
       <c r="L1261" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1262">
@@ -66112,7 +66112,7 @@
         <v>0</v>
       </c>
       <c r="I1282" t="n">
-        <v>144.998</v>
+        <v>146.151</v>
       </c>
       <c r="J1282" t="inlineStr">
         <is>
@@ -66120,10 +66120,10 @@
         </is>
       </c>
       <c r="K1282" t="n">
-        <v>0.04865083784741553</v>
+        <v>0.05698953504350168</v>
       </c>
       <c r="L1282" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1283">
@@ -67188,7 +67188,7 @@
         <v>0</v>
       </c>
       <c r="I1303" t="n">
-        <v>135.015</v>
+        <v>134.447</v>
       </c>
       <c r="J1303" t="inlineStr">
         <is>
@@ -67196,10 +67196,10 @@
         </is>
       </c>
       <c r="K1303" t="n">
-        <v>0.06064652971444273</v>
+        <v>0.0561844534349345</v>
       </c>
       <c r="L1303" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1304">
@@ -68264,7 +68264,7 @@
         <v>0</v>
       </c>
       <c r="I1324" t="n">
-        <v>118.001</v>
+        <v>118.829</v>
       </c>
       <c r="J1324" t="inlineStr">
         <is>
@@ -68272,10 +68272,10 @@
         </is>
       </c>
       <c r="K1324" t="n">
-        <v>0.003179542111930056</v>
+        <v>0.0102187422955613</v>
       </c>
       <c r="L1324" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1325">
@@ -69340,7 +69340,7 @@
         <v>0</v>
       </c>
       <c r="I1345" t="n">
-        <v>154.653</v>
+        <v>153.891</v>
       </c>
       <c r="J1345" t="inlineStr">
         <is>
@@ -69348,10 +69348,10 @@
         </is>
       </c>
       <c r="K1345" t="n">
-        <v>0.07409851094566045</v>
+        <v>0.06880625625069436</v>
       </c>
       <c r="L1345" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1346">
@@ -70416,7 +70416,7 @@
         <v>0</v>
       </c>
       <c r="I1366" t="n">
-        <v>110.409</v>
+        <v>109.059</v>
       </c>
       <c r="J1366" t="inlineStr">
         <is>
@@ -70424,10 +70424,10 @@
         </is>
       </c>
       <c r="K1366" t="n">
-        <v>0.02790191040107248</v>
+        <v>0.0153334822924811</v>
       </c>
       <c r="L1366" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1367">
@@ -71492,7 +71492,7 @@
         <v>0</v>
       </c>
       <c r="I1387" t="n">
-        <v>82.386</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="J1387" t="inlineStr">
         <is>
@@ -71500,10 +71500,10 @@
         </is>
       </c>
       <c r="K1387" t="n">
-        <v>-0.04793491575565689</v>
+        <v>-0.03621697829754777</v>
       </c>
       <c r="L1387" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1388">
@@ -72568,7 +72568,7 @@
         <v>0</v>
       </c>
       <c r="I1408" t="n">
-        <v>164.83</v>
+        <v>164.572</v>
       </c>
       <c r="J1408" t="inlineStr">
         <is>
@@ -72576,10 +72576,10 @@
         </is>
       </c>
       <c r="K1408" t="n">
-        <v>0.06603974931929457</v>
+        <v>0.0643711316203055</v>
       </c>
       <c r="L1408" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1409">
@@ -73644,7 +73644,7 @@
         <v>0</v>
       </c>
       <c r="I1429" t="n">
-        <v>138.56</v>
+        <v>137.926</v>
       </c>
       <c r="J1429" t="inlineStr">
         <is>
@@ -73652,10 +73652,10 @@
         </is>
       </c>
       <c r="K1429" t="n">
-        <v>0.0414443124934234</v>
+        <v>0.03667904333839411</v>
       </c>
       <c r="L1429" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1430">
@@ -74720,7 +74720,7 @@
         <v>0</v>
       </c>
       <c r="I1450" t="n">
-        <v>184.446</v>
+        <v>182.511</v>
       </c>
       <c r="J1450" t="inlineStr">
         <is>
@@ -74728,10 +74728,10 @@
         </is>
       </c>
       <c r="K1450" t="n">
-        <v>0.06118104618783504</v>
+        <v>0.05004832807861348</v>
       </c>
       <c r="L1450" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1451">
@@ -75796,7 +75796,7 @@
         <v>0</v>
       </c>
       <c r="I1471" t="n">
-        <v>119.367</v>
+        <v>118.136</v>
       </c>
       <c r="J1471" t="inlineStr">
         <is>
@@ -75804,10 +75804,10 @@
         </is>
       </c>
       <c r="K1471" t="n">
-        <v>0.03817251996034043</v>
+        <v>0.02746612395414783</v>
       </c>
       <c r="L1471" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1472">
@@ -76872,7 +76872,7 @@
         <v>0</v>
       </c>
       <c r="I1492" t="n">
-        <v>118.963</v>
+        <v>118.765</v>
       </c>
       <c r="J1492" t="inlineStr">
         <is>
@@ -76880,10 +76880,10 @@
         </is>
       </c>
       <c r="K1492" t="n">
-        <v>0.027456297934084</v>
+        <v>0.0257462170938989</v>
       </c>
       <c r="L1492" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1493">
@@ -77948,7 +77948,7 @@
         <v>0</v>
       </c>
       <c r="I1513" t="n">
-        <v>128.656</v>
+        <v>128.65</v>
       </c>
       <c r="J1513" t="inlineStr">
         <is>
@@ -77956,10 +77956,10 @@
         </is>
       </c>
       <c r="K1513" t="n">
-        <v>0.01942078364565591</v>
+        <v>0.01937324194762491</v>
       </c>
       <c r="L1513" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1514">
@@ -79024,7 +79024,7 @@
         <v>0</v>
       </c>
       <c r="I1534" t="n">
-        <v>185.231</v>
+        <v>184.393</v>
       </c>
       <c r="J1534" t="inlineStr">
         <is>
@@ -79032,7 +79032,7 @@
         </is>
       </c>
       <c r="K1534" t="n">
-        <v>0.05603698931597134</v>
+        <v>0.05125939270931923</v>
       </c>
       <c r="L1534" t="n">
         <v>69</v>
@@ -80100,7 +80100,7 @@
         <v>0</v>
       </c>
       <c r="I1555" t="n">
-        <v>144.129</v>
+        <v>146.415</v>
       </c>
       <c r="J1555" t="inlineStr">
         <is>
@@ -80108,10 +80108,10 @@
         </is>
       </c>
       <c r="K1555" t="n">
-        <v>0.008416943033457969</v>
+        <v>0.02441123378531551</v>
       </c>
       <c r="L1555" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1556">
@@ -81176,7 +81176,7 @@
         <v>0</v>
       </c>
       <c r="I1576" t="n">
-        <v>344.794</v>
+        <v>345.57</v>
       </c>
       <c r="J1576" t="inlineStr">
         <is>
@@ -81184,10 +81184,10 @@
         </is>
       </c>
       <c r="K1576" t="n">
-        <v>0.1119374105081203</v>
+        <v>0.1144399582048734</v>
       </c>
       <c r="L1576" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1577">
@@ -82252,7 +82252,7 @@
         <v>0</v>
       </c>
       <c r="I1597" t="n">
-        <v>141.786</v>
+        <v>142.812</v>
       </c>
       <c r="J1597" t="inlineStr">
         <is>
@@ -82260,10 +82260,10 @@
         </is>
       </c>
       <c r="K1597" t="n">
-        <v>0.04050136863657383</v>
+        <v>0.04803070442586987</v>
       </c>
       <c r="L1597" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1598">
@@ -83328,7 +83328,7 @@
         <v>0</v>
       </c>
       <c r="I1618" t="n">
-        <v>109.711</v>
+        <v>109.712</v>
       </c>
       <c r="J1618" t="inlineStr">
         <is>
@@ -83336,7 +83336,7 @@
         </is>
       </c>
       <c r="K1618" t="n">
-        <v>0.003943997071742311</v>
+        <v>0.003953147877013174</v>
       </c>
       <c r="L1618" t="n">
         <v>15</v>
@@ -84404,7 +84404,7 @@
         <v>0</v>
       </c>
       <c r="I1639" t="n">
-        <v>113.076</v>
+        <v>113.077</v>
       </c>
       <c r="J1639" t="inlineStr">
         <is>
@@ -84412,10 +84412,10 @@
         </is>
       </c>
       <c r="K1639" t="n">
-        <v>0.009219674589220128</v>
+        <v>0.009228599734030674</v>
       </c>
       <c r="L1639" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1640">
@@ -85480,7 +85480,7 @@
         <v>0</v>
       </c>
       <c r="I1660" t="n">
-        <v>114.208</v>
+        <v>113.735</v>
       </c>
       <c r="J1660" t="inlineStr">
         <is>
@@ -85488,10 +85488,10 @@
         </is>
       </c>
       <c r="K1660" t="n">
-        <v>0.02491205398808249</v>
+        <v>0.02066731280063183</v>
       </c>
       <c r="L1660" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1661">
@@ -88708,7 +88708,7 @@
         <v>0</v>
       </c>
       <c r="I1723" t="n">
-        <v>125.907</v>
+        <v>126.365</v>
       </c>
       <c r="J1723" t="inlineStr">
         <is>
@@ -88716,10 +88716,10 @@
         </is>
       </c>
       <c r="K1723" t="n">
-        <v>0.02495909346228053</v>
+        <v>0.02868749033303208</v>
       </c>
       <c r="L1723" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1724">
@@ -89784,7 +89784,7 @@
         <v>0</v>
       </c>
       <c r="I1744" t="n">
-        <v>188.869</v>
+        <v>188.712</v>
       </c>
       <c r="J1744" t="inlineStr">
         <is>
@@ -89792,7 +89792,7 @@
         </is>
       </c>
       <c r="K1744" t="n">
-        <v>0.1239793853698017</v>
+        <v>0.1230450617724772</v>
       </c>
       <c r="L1744" t="n">
         <v>91</v>
@@ -90860,7 +90860,7 @@
         <v>0</v>
       </c>
       <c r="I1765" t="n">
-        <v>109.006</v>
+        <v>108.278</v>
       </c>
       <c r="J1765" t="inlineStr">
         <is>
@@ -90868,10 +90868,10 @@
         </is>
       </c>
       <c r="K1765" t="n">
-        <v>0.04841688146808765</v>
+        <v>0.04141499634516999</v>
       </c>
       <c r="L1765" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1766">
@@ -91936,7 +91936,7 @@
         <v>0</v>
       </c>
       <c r="I1786" t="n">
-        <v>273.576</v>
+        <v>272.409</v>
       </c>
       <c r="J1786" t="inlineStr">
         <is>
@@ -91944,10 +91944,10 @@
         </is>
       </c>
       <c r="K1786" t="n">
-        <v>0.06946252448134738</v>
+        <v>0.064900491386084</v>
       </c>
       <c r="L1786" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1787">
@@ -93012,7 +93012,7 @@
         <v>0</v>
       </c>
       <c r="I1807" t="n">
-        <v>146.106</v>
+        <v>145.957</v>
       </c>
       <c r="J1807" t="inlineStr">
         <is>
@@ -93020,7 +93020,7 @@
         </is>
       </c>
       <c r="K1807" t="n">
-        <v>0.02754061467051128</v>
+        <v>0.02649272100710309</v>
       </c>
       <c r="L1807" t="n">
         <v>42</v>
@@ -94099,7 +94099,7 @@
         <v>0.03552060470655394</v>
       </c>
       <c r="L1828" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="1829">
@@ -96240,7 +96240,7 @@
         <v>0</v>
       </c>
       <c r="I1870" t="n">
-        <v>139.203</v>
+        <v>139.709</v>
       </c>
       <c r="J1870" t="inlineStr">
         <is>
@@ -96248,10 +96248,10 @@
         </is>
       </c>
       <c r="K1870" t="n">
-        <v>0.02896108215988469</v>
+        <v>0.03270133422034971</v>
       </c>
       <c r="L1870" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1871">
@@ -97316,7 +97316,7 @@
         <v>0</v>
       </c>
       <c r="I1891" t="n">
-        <v>128.762</v>
+        <v>126.893</v>
       </c>
       <c r="J1891" t="inlineStr">
         <is>
@@ -97324,10 +97324,10 @@
         </is>
       </c>
       <c r="K1891" t="n">
-        <v>0.112501187997339</v>
+        <v>0.09635306416913636</v>
       </c>
       <c r="L1891" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1892">
@@ -98392,7 +98392,7 @@
         <v>0</v>
       </c>
       <c r="I1912" t="n">
-        <v>104.024</v>
+        <v>103.203</v>
       </c>
       <c r="J1912" t="inlineStr">
         <is>
@@ -98400,10 +98400,10 @@
         </is>
       </c>
       <c r="K1912" t="n">
-        <v>0.02427160566764153</v>
+        <v>0.01618763477387541</v>
       </c>
       <c r="L1912" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1913">
@@ -99033,7 +99033,7 @@
         <v>0</v>
       </c>
       <c r="L1933" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
